--- a/packages/calculators/src/modules/test/5.4-atmospheric-deposition.xlsx
+++ b/packages/calculators/src/modules/test/5.4-atmospheric-deposition.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37215E9-791F-AA4D-A3A1-73B5F5AA8303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364905C5-BECA-2443-B465-EBB315309601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -16,6 +11,9 @@
     <sheet name="5.4.1.1" sheetId="1" r:id="rId1"/>
     <sheet name="5.4.1.3 (feedlot local)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -841,6 +839,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1259,7 +1279,7 @@
       </c>
       <c r="I5">
         <f>IF(ISBLANK(A5), "", G5*H5*$L$10/1000)</f>
-        <v>3.1244714285714288E-4</v>
+        <v>3.1216310000000005E-4</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17">
@@ -1294,7 +1314,7 @@
       </c>
       <c r="I6">
         <f>IF(ISBLANK(A6), "", G6*H6*$L$10/1000)</f>
-        <v>1.518E-3</v>
+        <v>1.51662E-3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17">
@@ -1329,7 +1349,7 @@
       </c>
       <c r="I7">
         <f>IF(ISBLANK(A9), "", G7*H7*$L$10/1000)</f>
-        <v>3.9034285714285708E-4</v>
+        <v>3.8998800000000002E-4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1364,7 +1384,7 @@
       </c>
       <c r="I8">
         <f>IF(ISBLANK(A8), "", G8*H8*$L$10/1000)</f>
-        <v>1.8456428571428572E-4</v>
+        <v>1.8439650000000001E-4</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -1401,7 +1421,7 @@
       </c>
       <c r="I9">
         <f>IF(ISBLANK(A9), "", G9*H9*$L$10/1000)</f>
-        <v>1.5085714285714283E-3</v>
+        <v>1.5072E-3</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1438,14 +1458,14 @@
       </c>
       <c r="I10">
         <f>IF(ISBLANK(A10), "", G10*H10*$L$10/1000)</f>
-        <v>1.1708022857142856E-3</v>
+        <v>1.1697379199999999E-3</v>
       </c>
       <c r="K10" t="s">
         <v>6</v>
       </c>
       <c r="L10">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1480,7 +1500,7 @@
       </c>
       <c r="I11">
         <f>IF(ISBLANK(#REF!), "", G11*H11*$L$10/1000)</f>
-        <v>3.1093302239999993E-4</v>
+        <v>3.1065035601599998E-4</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1517,7 +1537,7 @@
       </c>
       <c r="I12">
         <f>IF(ISBLANK(#REF!), "", G12*H12*$L$10/1000)</f>
-        <v>6.939428571428572E-5</v>
+        <v>6.9331199999999991E-5</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>18</v>
@@ -1556,7 +1576,7 @@
       </c>
       <c r="I13">
         <f>IF(ISBLANK(#REF!), "", G13*H13*$L$10/1000)</f>
-        <v>6.0672857142857152E-6</v>
+        <v>6.0617700000000014E-6</v>
       </c>
       <c r="K13" t="s">
         <v>120</v>
@@ -1594,7 +1614,7 @@
       </c>
       <c r="I14">
         <f>IF(ISBLANK(#REF!), "", G14*H14*$L$10/1000)</f>
-        <v>2.7154285714285714E-5</v>
+        <v>2.7129599999999999E-5</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>8</v>
@@ -1635,7 +1655,7 @@
       </c>
       <c r="I15">
         <f>IF(ISBLANK(#REF!), "", G15*H15*$L$10/1000)</f>
-        <v>1.4708571428571428E-5</v>
+        <v>1.46952E-5</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>9</v>
@@ -1676,7 +1696,7 @@
       </c>
       <c r="I16">
         <f>IF(ISBLANK(#REF!), "", G16*H16*$L$10/1000)</f>
-        <v>6.6527999999999992E-6</v>
+        <v>6.646752E-6</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>10</v>
@@ -2141,8 +2161,8 @@
         <v>6</v>
       </c>
       <c r="AJ7">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="AM7" s="8"/>
     </row>
@@ -2323,7 +2343,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="F11">
-        <f>IF(ISBLANK(H11),"",C11*(D11)/6.25)</f>
+        <f t="shared" ref="F11:F20" si="0">IF(ISBLANK(H11),"",C11*(D11)/6.25)</f>
         <v>0.23296000000000003</v>
       </c>
       <c r="G11">
@@ -2334,7 +2354,7 @@
         <v>500</v>
       </c>
       <c r="I11">
-        <f>IF(ISBLANK(H11),"",H11*G11*A11)</f>
+        <f t="shared" ref="I11:I20" si="1">IF(ISBLANK(H11),"",H11*G11*A11)</f>
         <v>5563.0848000000015</v>
       </c>
       <c r="J11">
@@ -2353,31 +2373,31 @@
         <v>1</v>
       </c>
       <c r="O11">
-        <f>IF(ISBLANK(I11),"",I11)</f>
+        <f t="shared" ref="O11:O20" si="2">IF(ISBLANK(I11),"",I11)</f>
         <v>5563.0848000000015</v>
       </c>
       <c r="P11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" ref="P11:P20" si="3">IF(ISBLANK(I11),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
         <v>0.6</v>
       </c>
       <c r="Q11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" ref="Q11:Q20" si="4">IF(ISBLANK(I11),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP(K11,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" ref="R11:R20" si="5">IF(ISBLANK(I11),"",VLOOKUP(K11,$AI$49:$AK$52, 2,FALSE))</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP(K11,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" ref="S11:S20" si="6">IF(ISBLANK(I11),"",VLOOKUP(K11,$AI$49:$AK$52, 3,FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="T11">
-        <f>IF(ISBLANK(I11),"", (O11*(1-P11-Q11))-Y11)</f>
+        <f t="shared" ref="T11:T20" si="7">IF(ISBLANK(I11),"", (O11*(1-P11-Q11))-Y11)</f>
         <v>2083.9315660800007</v>
       </c>
       <c r="U11">
-        <f>IF(ISBLANK(I11),"",T11*N11)</f>
+        <f t="shared" ref="U11:U20" si="8">IF(ISBLANK(I11),"",T11*N11)</f>
         <v>2083.9315660800007</v>
       </c>
       <c r="V11" cm="1">
@@ -2385,11 +2405,11 @@
         <v>0.02</v>
       </c>
       <c r="W11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" ref="W11:W20" si="9">IF(ISBLANK(I11),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="X11">
-        <f>IF(ISBLANK(I11),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" ref="X11:X20" si="10">IF(ISBLANK(I11),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
         <v>0.35</v>
       </c>
       <c r="Y11" cm="1">
@@ -2397,11 +2417,11 @@
         <v>111.26169600000003</v>
       </c>
       <c r="Z11">
-        <f>IF(ISBLANK(I11),"", U11*(1-R11-S11))</f>
+        <f t="shared" ref="Z11:Z20" si="11">IF(ISBLANK(I11),"", U11*(1-R11-S11))</f>
         <v>1552.5290167296005</v>
       </c>
       <c r="AA11">
-        <f>IF(ISBLANK(I11),"", Y11*(1-W11-X11))</f>
+        <f t="shared" ref="AA11:AA20" si="12">IF(ISBLANK(I11),"", Y11*(1-W11-X11))</f>
         <v>72.320102400000025</v>
       </c>
       <c r="AB11" cm="1">
@@ -2413,19 +2433,19 @@
         <v>324.96982382592</v>
       </c>
       <c r="AD11">
-        <f>IF(ISBLANK(A11), "", AB11*$AJ$6)</f>
+        <f t="shared" ref="AD11:AD20" si="13">IF(ISBLANK(A11), "", AB11*$AJ$6)</f>
         <v>272.97465201377287</v>
       </c>
       <c r="AE11" t="s">
         <v>11</v>
       </c>
       <c r="AF11">
-        <f>IF(ISBLANK(A11),"",VLOOKUP(AE11,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" ref="AF11:AF20" si="14">IF(ISBLANK(A11),"",VLOOKUP(AE11,$AI$11:$AJ$25,2,FALSE))</f>
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="AG11">
-        <f>IF(ISBLANK(A11), "", AD11*AF11*$AJ$7/1000)</f>
-        <v>8.5363073322592686E-3</v>
+        <f t="shared" ref="AG11:AG20" si="15">IF(ISBLANK(A11), "", AD11*AF11*$AJ$7/1000)</f>
+        <v>8.528547052866306E-3</v>
       </c>
       <c r="AI11" s="2" t="s">
         <v>8</v>
@@ -2454,18 +2474,18 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="F12">
-        <f>IF(ISBLANK(H12),"",C12*(D12)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.23296000000000003</v>
       </c>
       <c r="G12">
-        <f t="shared" ref="G12:G20" si="0">IF(ISBLANK(H12), "", F12*(1-E12))</f>
+        <f t="shared" ref="G12:G20" si="16">IF(ISBLANK(H12), "", F12*(1-E12))</f>
         <v>0.18543616000000004</v>
       </c>
       <c r="H12">
         <v>500</v>
       </c>
       <c r="I12">
-        <f>IF(ISBLANK(H12),"",H12*G12*A12)</f>
+        <f t="shared" si="1"/>
         <v>7417.4464000000025</v>
       </c>
       <c r="J12">
@@ -2484,31 +2504,31 @@
         <v>1</v>
       </c>
       <c r="O12">
-        <f>IF(ISBLANK(I12),"",I12)</f>
+        <f t="shared" si="2"/>
         <v>7417.4464000000025</v>
       </c>
       <c r="P12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP(K12,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP(K12,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T12">
-        <f>IF(ISBLANK(I12),"", (O12*(1-P12-Q12))-Y12)</f>
+        <f t="shared" si="7"/>
         <v>2778.5754214400013</v>
       </c>
       <c r="U12">
-        <f>IF(ISBLANK(I12),"",T12*N12)</f>
+        <f t="shared" si="8"/>
         <v>2778.5754214400013</v>
       </c>
       <c r="V12" cm="1">
@@ -2516,11 +2536,11 @@
         <v>0.02</v>
       </c>
       <c r="W12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IF(ISBLANK(I12),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y12" cm="1">
@@ -2528,11 +2548,11 @@
         <v>148.34892800000006</v>
       </c>
       <c r="Z12">
-        <f>IF(ISBLANK(I12),"", U12*(1-R12-S12))</f>
+        <f t="shared" si="11"/>
         <v>2070.0386889728011</v>
       </c>
       <c r="AA12">
-        <f>IF(ISBLANK(I12),"", Y12*(1-W12-X12))</f>
+        <f t="shared" si="12"/>
         <v>96.426803200000037</v>
       </c>
       <c r="AB12" cm="1">
@@ -2544,19 +2564,19 @@
         <v>541.61637304320027</v>
       </c>
       <c r="AD12">
-        <f>IF(ISBLANK(A12), "", AB12*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>341.21831501721613</v>
       </c>
       <c r="AE12" t="s">
         <v>11</v>
       </c>
       <c r="AF12">
-        <f>IF(ISBLANK(A12),"",VLOOKUP(AE12,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="AG12">
-        <f>IF(ISBLANK(A12), "", AD12*AF12*$AJ$7/1000)</f>
-        <v>1.0670384165324088E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.0660683816082886E-2</v>
       </c>
       <c r="AI12" s="2" t="s">
         <v>9</v>
@@ -2585,18 +2605,18 @@
         <v>0.127</v>
       </c>
       <c r="F13">
-        <f>IF(ISBLANK(H13),"",C13*(D13)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H13">
         <v>500</v>
       </c>
       <c r="I13">
-        <f>IF(ISBLANK(H13),"",H13*G13*A13)</f>
+        <f t="shared" si="1"/>
         <v>9051.264000000001</v>
       </c>
       <c r="J13">
@@ -2615,31 +2635,31 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <f>IF(ISBLANK(I13),"",I13)</f>
+        <f t="shared" si="2"/>
         <v>9051.264000000001</v>
       </c>
       <c r="P13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP(K13,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP(K13,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T13">
-        <f>IF(ISBLANK(I13),"", (O13*(1-P13-Q13))-Y13)</f>
+        <f t="shared" si="7"/>
         <v>3390.6034944000007</v>
       </c>
       <c r="U13">
-        <f>IF(ISBLANK(I13),"",T13*N13)</f>
+        <f t="shared" si="8"/>
         <v>3390.6034944000007</v>
       </c>
       <c r="V13" cm="1">
@@ -2647,11 +2667,11 @@
         <v>0.02</v>
       </c>
       <c r="W13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IF(ISBLANK(I13),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y13" cm="1">
@@ -2659,11 +2679,11 @@
         <v>181.02528000000004</v>
       </c>
       <c r="Z13">
-        <f>IF(ISBLANK(I13),"", U13*(1-R13-S13))</f>
+        <f t="shared" si="11"/>
         <v>2525.9996033280004</v>
       </c>
       <c r="AA13">
-        <f>IF(ISBLANK(I13),"", Y13*(1-W13-X13))</f>
+        <f t="shared" si="12"/>
         <v>117.66643200000003</v>
       </c>
       <c r="AB13" cm="1">
@@ -2675,19 +2695,19 @@
         <v>793.09981059840027</v>
       </c>
       <c r="AD13">
-        <f>IF(ISBLANK(A13), "", AB13*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>388.61890719321605</v>
       </c>
       <c r="AE13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="AF13">
-        <f>IF(ISBLANK(A13),"",VLOOKUP(AE13,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="AG13">
-        <f>IF(ISBLANK(A13), "", AD13*AF13*$AJ$7/1000)</f>
-        <v>1.2152668397799285E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.2141620517437651E-2</v>
       </c>
       <c r="AI13" s="2" t="s">
         <v>10</v>
@@ -2716,18 +2736,18 @@
         <v>0.127</v>
       </c>
       <c r="F14">
-        <f>IF(ISBLANK(H14),"",C14*(D14)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H14">
         <v>500</v>
       </c>
       <c r="I14">
-        <f>IF(ISBLANK(H14),"",H14*G14*A14)</f>
+        <f t="shared" si="1"/>
         <v>10861.516800000001</v>
       </c>
       <c r="J14">
@@ -2746,31 +2766,31 @@
         <v>1</v>
       </c>
       <c r="O14">
-        <f>IF(ISBLANK(I14),"",I14)</f>
+        <f t="shared" si="2"/>
         <v>10861.516800000001</v>
       </c>
       <c r="P14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP(K14,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP(K14,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T14">
-        <f>IF(ISBLANK(I14),"", (O14*(1-P14-Q14))-Y14)</f>
+        <f t="shared" si="7"/>
         <v>4068.7241932800002</v>
       </c>
       <c r="U14">
-        <f>IF(ISBLANK(I14),"",T14*N14)</f>
+        <f t="shared" si="8"/>
         <v>4068.7241932800002</v>
       </c>
       <c r="V14" cm="1">
@@ -2778,11 +2798,11 @@
         <v>0.02</v>
       </c>
       <c r="W14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IF(ISBLANK(I14),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y14" cm="1">
@@ -2790,11 +2810,11 @@
         <v>217.23033600000002</v>
       </c>
       <c r="Z14">
-        <f>IF(ISBLANK(I14),"", U14*(1-R14-S14))</f>
+        <f t="shared" si="11"/>
         <v>3031.1995239936</v>
       </c>
       <c r="AA14">
-        <f>IF(ISBLANK(I14),"", Y14*(1-W14-X14))</f>
+        <f t="shared" si="12"/>
         <v>141.19971840000002</v>
       </c>
       <c r="AB14" cm="1">
@@ -2806,19 +2826,19 @@
         <v>1110.33973483776</v>
       </c>
       <c r="AD14">
-        <f>IF(ISBLANK(A14), "", AB14*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>433.03249658672644</v>
       </c>
       <c r="AE14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="AF14">
-        <f>IF(ISBLANK(A14),"",VLOOKUP(AE14,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="AG14">
-        <f>IF(ISBLANK(A14), "", AD14*AF14*$AJ$7/1000)</f>
-        <v>4.7633574624539911E-3</v>
+        <f t="shared" si="15"/>
+        <v>4.7590271374881241E-3</v>
       </c>
       <c r="AI14" s="2" t="s">
         <v>118</v>
@@ -2847,18 +2867,18 @@
         <v>0.127</v>
       </c>
       <c r="F15">
-        <f>IF(ISBLANK(H15),"",C15*(D15)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H15">
         <v>500</v>
       </c>
       <c r="I15">
-        <f>IF(ISBLANK(H15),"",H15*G15*A15)</f>
+        <f t="shared" si="1"/>
         <v>12671.769600000001</v>
       </c>
       <c r="J15">
@@ -2877,31 +2897,31 @@
         <v>1</v>
       </c>
       <c r="O15">
-        <f>IF(ISBLANK(I15),"",I15)</f>
+        <f t="shared" si="2"/>
         <v>12671.769600000001</v>
       </c>
       <c r="P15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP(K15,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>0.01</v>
       </c>
       <c r="S15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP(K15,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="T15">
-        <f>IF(ISBLANK(I15),"", (O15*(1-P15-Q15))-Y15)</f>
+        <f t="shared" si="7"/>
         <v>4746.8448921600002</v>
       </c>
       <c r="U15">
-        <f>IF(ISBLANK(I15),"",T15*N15)</f>
+        <f t="shared" si="8"/>
         <v>4746.8448921600002</v>
       </c>
       <c r="V15" cm="1">
@@ -2909,11 +2929,11 @@
         <v>0.02</v>
       </c>
       <c r="W15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X15">
-        <f>IF(ISBLANK(I15),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y15" cm="1">
@@ -2921,11 +2941,11 @@
         <v>253.43539200000004</v>
       </c>
       <c r="Z15">
-        <f>IF(ISBLANK(I15),"", U15*(1-R15-S15))</f>
+        <f t="shared" si="11"/>
         <v>2800.6384863744001</v>
       </c>
       <c r="AA15">
-        <f>IF(ISBLANK(I15),"", Y15*(1-W15-X15))</f>
+        <f t="shared" si="12"/>
         <v>164.73300480000003</v>
       </c>
       <c r="AB15" cm="1">
@@ -2937,19 +2957,19 @@
         <v>1186.1485964697602</v>
       </c>
       <c r="AD15">
-        <f>IF(ISBLANK(A15), "", AB15*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>373.63680788797438</v>
       </c>
       <c r="AE15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="AF15">
-        <f>IF(ISBLANK(A15),"",VLOOKUP(AE15,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>1.8E-3</v>
       </c>
       <c r="AG15">
-        <f>IF(ISBLANK(A15), "", AD15*AF15*$AJ$7/1000)</f>
-        <v>1.0568583994545562E-3</v>
+        <f t="shared" si="15"/>
+        <v>1.0558976190914158E-3</v>
       </c>
       <c r="AI15" s="2" t="s">
         <v>119</v>
@@ -2978,18 +2998,18 @@
         <v>0.127</v>
       </c>
       <c r="F16">
-        <f>IF(ISBLANK(H16),"",C16*(D16)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H16">
         <v>500</v>
       </c>
       <c r="I16">
-        <f>IF(ISBLANK(H16),"",H16*G16*A16)</f>
+        <f t="shared" si="1"/>
         <v>14482.022400000002</v>
       </c>
       <c r="J16">
@@ -3008,31 +3028,31 @@
         <v>1</v>
       </c>
       <c r="O16">
-        <f>IF(ISBLANK(I16),"",I16)</f>
+        <f t="shared" si="2"/>
         <v>14482.022400000002</v>
       </c>
       <c r="P16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP(K16,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP(K16,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T16">
-        <f>IF(ISBLANK(I16),"", (O16*(1-P16-Q16))-Y16)</f>
+        <f t="shared" si="7"/>
         <v>5424.9655910400006</v>
       </c>
       <c r="U16">
-        <f>IF(ISBLANK(I16),"",T16*N16)</f>
+        <f t="shared" si="8"/>
         <v>5424.9655910400006</v>
       </c>
       <c r="V16" cm="1">
@@ -3040,11 +3060,11 @@
         <v>0.02</v>
       </c>
       <c r="W16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IF(ISBLANK(I16),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y16" cm="1">
@@ -3052,11 +3072,11 @@
         <v>289.64044800000005</v>
       </c>
       <c r="Z16">
-        <f>IF(ISBLANK(I16),"", U16*(1-R16-S16))</f>
+        <f t="shared" si="11"/>
         <v>4041.5993653248006</v>
       </c>
       <c r="AA16">
-        <f>IF(ISBLANK(I16),"", Y16*(1-W16-X16))</f>
+        <f t="shared" si="12"/>
         <v>188.26629120000004</v>
       </c>
       <c r="AB16" cm="1">
@@ -3068,19 +3088,19 @@
         <v>1903.43954543616</v>
       </c>
       <c r="AD16">
-        <f>IF(ISBLANK(A16), "", AB16*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>488.54948332861449</v>
       </c>
       <c r="AE16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AF16">
-        <f>IF(ISBLANK(A16),"",VLOOKUP(AE16,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="AG16">
-        <f>IF(ISBLANK(A16), "", AD16*AF16*$AJ$7/1000)</f>
-        <v>1.9960736033140533E-3</v>
+        <f t="shared" si="15"/>
+        <v>1.9942589909474045E-3</v>
       </c>
       <c r="AI16" s="2" t="s">
         <v>11</v>
@@ -3109,18 +3129,18 @@
         <v>0.127</v>
       </c>
       <c r="F17">
-        <f>IF(ISBLANK(H17),"",C17*(D17)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H17">
         <v>500</v>
       </c>
       <c r="I17">
-        <f>IF(ISBLANK(H17),"",H17*G17*A17)</f>
+        <f t="shared" si="1"/>
         <v>16292.2752</v>
       </c>
       <c r="J17">
@@ -3139,31 +3159,31 @@
         <v>1</v>
       </c>
       <c r="O17">
-        <f>IF(ISBLANK(I17),"",I17)</f>
+        <f t="shared" si="2"/>
         <v>16292.2752</v>
       </c>
       <c r="P17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP(K17,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP(K17,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T17">
-        <f>IF(ISBLANK(I17),"", (O17*(1-P17-Q17))-Y17)</f>
+        <f t="shared" si="7"/>
         <v>6103.0862899200001</v>
       </c>
       <c r="U17">
-        <f>IF(ISBLANK(I17),"",T17*N17)</f>
+        <f t="shared" si="8"/>
         <v>6103.0862899200001</v>
       </c>
       <c r="V17" cm="1">
@@ -3171,11 +3191,11 @@
         <v>0.02</v>
       </c>
       <c r="W17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IF(ISBLANK(I17),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y17" cm="1">
@@ -3183,11 +3203,11 @@
         <v>325.84550400000001</v>
       </c>
       <c r="Z17">
-        <f>IF(ISBLANK(I17),"", U17*(1-R17-S17))</f>
+        <f t="shared" si="11"/>
         <v>4546.7992859903998</v>
       </c>
       <c r="AA17">
-        <f>IF(ISBLANK(I17),"", Y17*(1-W17-X17))</f>
+        <f t="shared" si="12"/>
         <v>211.79957760000002</v>
       </c>
       <c r="AB17" cm="1">
@@ -3199,19 +3219,19 @@
         <v>2379.2994317951998</v>
       </c>
       <c r="AD17">
-        <f>IF(ISBLANK(A17), "", AB17*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>499.65288067699191</v>
       </c>
       <c r="AE17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AF17">
-        <f>IF(ISBLANK(A17),"",VLOOKUP(AE17,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>6.4000000000000003E-3</v>
       </c>
       <c r="AG17">
-        <f>IF(ISBLANK(A17), "", AD17*AF17*$AJ$7/1000)</f>
-        <v>5.0250803999514621E-3</v>
+        <f t="shared" si="15"/>
+        <v>5.0205121450424151E-3</v>
       </c>
       <c r="AI17" s="2" t="s">
         <v>12</v>
@@ -3240,18 +3260,18 @@
         <v>0.127</v>
       </c>
       <c r="F18">
-        <f>IF(ISBLANK(H18),"",C18*(D18)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.20736000000000002</v>
       </c>
       <c r="G18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.18102528000000001</v>
       </c>
       <c r="H18">
         <v>500</v>
       </c>
       <c r="I18">
-        <f>IF(ISBLANK(H18),"",H18*G18*A18)</f>
+        <f t="shared" si="1"/>
         <v>18102.528000000002</v>
       </c>
       <c r="J18">
@@ -3270,31 +3290,31 @@
         <v>1</v>
       </c>
       <c r="O18">
-        <f>IF(ISBLANK(I18),"",I18)</f>
+        <f t="shared" si="2"/>
         <v>18102.528000000002</v>
       </c>
       <c r="P18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP(K18,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP(K18,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T18">
-        <f>IF(ISBLANK(I18),"", (O18*(1-P18-Q18))-Y18)</f>
+        <f t="shared" si="7"/>
         <v>6781.2069888000015</v>
       </c>
       <c r="U18">
-        <f>IF(ISBLANK(I18),"",T18*N18)</f>
+        <f t="shared" si="8"/>
         <v>6781.2069888000015</v>
       </c>
       <c r="V18" cm="1">
@@ -3302,11 +3322,11 @@
         <v>0.02</v>
       </c>
       <c r="W18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X18">
-        <f>IF(ISBLANK(I18),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y18" cm="1">
@@ -3314,11 +3334,11 @@
         <v>362.05056000000008</v>
       </c>
       <c r="Z18">
-        <f>IF(ISBLANK(I18),"", U18*(1-R18-S18))</f>
+        <f t="shared" si="11"/>
         <v>5051.9992066560008</v>
       </c>
       <c r="AA18">
-        <f>IF(ISBLANK(I18),"", Y18*(1-W18-X18))</f>
+        <f t="shared" si="12"/>
         <v>235.33286400000006</v>
       </c>
       <c r="AB18" cm="1">
@@ -3330,19 +3350,19 @@
         <v>2908.0326388608005</v>
       </c>
       <c r="AD18">
-        <f>IF(ISBLANK(A18), "", AB18*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>499.65288067699203</v>
       </c>
       <c r="AE18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="AF18">
-        <f>IF(ISBLANK(A18),"",VLOOKUP(AE18,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="AG18">
-        <f>IF(ISBLANK(A18), "", AD18*AF18*$AJ$7/1000)</f>
-        <v>4.6324959937052547E-3</v>
+        <f t="shared" si="15"/>
+        <v>4.6282846337109777E-3</v>
       </c>
       <c r="AI18" s="2" t="s">
         <v>13</v>
@@ -3371,18 +3391,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F19">
-        <f>IF(ISBLANK(H19),"",C19*(D19)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="G19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="H19">
         <v>500</v>
       </c>
       <c r="I19">
-        <f>IF(ISBLANK(H19),"",H19*G19*A19)</f>
+        <f t="shared" si="1"/>
         <v>16106.111999999996</v>
       </c>
       <c r="J19">
@@ -3401,31 +3421,31 @@
         <v>1</v>
       </c>
       <c r="O19">
-        <f>IF(ISBLANK(I19),"",I19)</f>
+        <f t="shared" si="2"/>
         <v>16106.111999999996</v>
       </c>
       <c r="P19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP(K19,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP(K19,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T19">
-        <f>IF(ISBLANK(I19),"", (O19*(1-P19-Q19))-Y19)</f>
+        <f t="shared" si="7"/>
         <v>6033.3495551999986</v>
       </c>
       <c r="U19">
-        <f>IF(ISBLANK(I19),"",T19*N19)</f>
+        <f t="shared" si="8"/>
         <v>6033.3495551999986</v>
       </c>
       <c r="V19" cm="1">
@@ -3433,11 +3453,11 @@
         <v>0.02</v>
       </c>
       <c r="W19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X19">
-        <f>IF(ISBLANK(I19),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y19" cm="1">
@@ -3445,11 +3465,11 @@
         <v>322.12223999999992</v>
       </c>
       <c r="Z19">
-        <f>IF(ISBLANK(I19),"", U19*(1-R19-S19))</f>
+        <f t="shared" si="11"/>
         <v>4494.8454186239987</v>
       </c>
       <c r="AA19">
-        <f>IF(ISBLANK(I19),"", Y19*(1-W19-X19))</f>
+        <f t="shared" si="12"/>
         <v>209.37945599999995</v>
       </c>
       <c r="AB19" cm="1">
@@ -3461,19 +3481,19 @@
         <v>2822.5349247743989</v>
       </c>
       <c r="AD19">
-        <f>IF(ISBLANK(A19), "", AB19*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>395.15488946841589</v>
       </c>
       <c r="AE19" s="2" t="s">
         <v>118</v>
       </c>
       <c r="AF19">
-        <f>IF(ISBLANK(A19),"",VLOOKUP(AE19,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="AG19">
-        <f>IF(ISBLANK(A19), "", AD19*AF19*$AJ$7/1000)</f>
-        <v>1.8007772820060667E-3</v>
+        <f t="shared" si="15"/>
+        <v>1.7991402117496975E-3</v>
       </c>
       <c r="AI19" s="2" t="s">
         <v>14</v>
@@ -3502,18 +3522,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F20">
-        <f>IF(ISBLANK(H20),"",C20*(D20)/6.25)</f>
+        <f t="shared" si="0"/>
         <v>0.15743999999999997</v>
       </c>
       <c r="G20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>0.14641919999999997</v>
       </c>
       <c r="H20">
         <v>500</v>
       </c>
       <c r="I20">
-        <f>IF(ISBLANK(H20),"",H20*G20*A20)</f>
+        <f t="shared" si="1"/>
         <v>17570.303999999996</v>
       </c>
       <c r="J20">
@@ -3532,31 +3552,31 @@
         <v>1</v>
       </c>
       <c r="O20">
-        <f>IF(ISBLANK(I20),"",I20)</f>
+        <f t="shared" si="2"/>
         <v>17570.303999999996</v>
       </c>
       <c r="P20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP("drylot",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP("drylot",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="4"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="R20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP(K20,$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP(K20,$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="T20">
-        <f>IF(ISBLANK(I20),"", (O20*(1-P20-Q20))-Y20)</f>
+        <f t="shared" si="7"/>
         <v>6581.8358783999993</v>
       </c>
       <c r="U20">
-        <f>IF(ISBLANK(I20),"",T20*N20)</f>
+        <f t="shared" si="8"/>
         <v>6581.8358783999993</v>
       </c>
       <c r="V20" cm="1">
@@ -3564,11 +3584,11 @@
         <v>0.02</v>
       </c>
       <c r="W20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 2,FALSE))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X20">
-        <f>IF(ISBLANK(I20),"",VLOOKUP("anaerobicLagoon",$AI$49:$AK$52, 3,FALSE))</f>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="Y20" cm="1">
@@ -3576,11 +3596,11 @@
         <v>351.40607999999992</v>
       </c>
       <c r="Z20">
-        <f>IF(ISBLANK(I20),"", U20*(1-R20-S20))</f>
+        <f t="shared" si="11"/>
         <v>4903.4677294079993</v>
       </c>
       <c r="AA20">
-        <f>IF(ISBLANK(I20),"", Y20*(1-W20-X20))</f>
+        <f t="shared" si="12"/>
         <v>228.41395199999997</v>
       </c>
       <c r="AB20" cm="1">
@@ -3592,19 +3612,19 @@
         <v>3335.7230929151997</v>
       </c>
       <c r="AD20">
-        <f>IF(ISBLANK(A20), "", AB20*$AJ$6)</f>
+        <f t="shared" si="13"/>
         <v>377.19330358348788</v>
       </c>
       <c r="AE20" s="2" t="s">
         <v>119</v>
       </c>
       <c r="AF20">
-        <f>IF(ISBLANK(A20),"",VLOOKUP(AE20,$AI$11:$AJ$25,2,FALSE))</f>
+        <f t="shared" si="14"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="AG20">
-        <f>IF(ISBLANK(A20), "", AD20*AF20*$AJ$7/1000)</f>
-        <v>4.7418586736209904E-3</v>
+        <f t="shared" si="15"/>
+        <v>4.7375478930086088E-3</v>
       </c>
       <c r="AI20" s="2" t="s">
         <v>15</v>
